--- a/Data/Master/Department.xlsx
+++ b/Data/Master/Department.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Department" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,6 +428,126 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SAL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LEG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Customer Success</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
